--- a/excel-files/QUEZON CITY/BALINGASA ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/QUEZON CITY/BALINGASA ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="347" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95D8E0D5-A079-4724-A716-CEB20FE6237E}"/>
+  <xr:revisionPtr revIDLastSave="451" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E6C5367E-AD46-4F73-B09B-C1F0625A1945}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -3540,7 +3540,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D2" s="1">
         <v>200</v>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="H2" s="4">
         <f>IF((D2-C2)&lt;0,0,D2-C2)</f>
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="29.25" customHeight="1">
@@ -3568,7 +3568,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -3577,7 +3577,7 @@
       <c r="F3" s="5"/>
       <c r="G3" s="3">
         <f>IF((C3-D3)&lt;0,0,C3-D3)</f>
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H3" s="4">
         <f>IF((D3-C3)&lt;0,0,D3-C3)</f>
@@ -3592,7 +3592,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D4" s="1">
         <v>200</v>
@@ -3609,7 +3609,7 @@
       </c>
       <c r="H4" s="4">
         <f>IF((D4-C4)&lt;0,0,D4-C4)</f>
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="25.5" customHeight="1">
@@ -3620,7 +3620,7 @@
         <v>12</v>
       </c>
       <c r="C5" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D5" s="1">
         <v>0</v>
@@ -3629,7 +3629,7 @@
       <c r="F5" s="5"/>
       <c r="G5" s="3">
         <f t="shared" ref="G5:G6" si="0">IF((C5-D5)&lt;0,0,C5-D5)</f>
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H5" s="4">
         <f t="shared" ref="H5:H6" si="1">IF((D5-C5)&lt;0,0,D5-C5)</f>
@@ -3644,7 +3644,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D6" s="1">
         <v>0</v>
@@ -3653,7 +3653,7 @@
       <c r="F6" s="5"/>
       <c r="G6" s="3">
         <f t="shared" si="0"/>
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="1"/>
@@ -3673,7 +3673,7 @@
         <v>8</v>
       </c>
       <c r="C8" s="1">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D8" s="1">
         <v>0</v>
@@ -3682,7 +3682,7 @@
       <c r="F8" s="5"/>
       <c r="G8" s="3">
         <f>IF((C8-D8)&lt;0,0,C8-D8)</f>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H8" s="4">
         <f>IF((D8-C8)&lt;0,0,D8-C8)</f>
@@ -3697,7 +3697,7 @@
         <v>10</v>
       </c>
       <c r="C9" s="1">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D9" s="1">
         <v>0</v>
@@ -3706,7 +3706,7 @@
       <c r="F9" s="5"/>
       <c r="G9" s="3">
         <f>IF((C9-D9)&lt;0,0,C9-D9)</f>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H9" s="4">
         <f>IF((D9-C9)&lt;0,0,D9-C9)</f>
@@ -3721,7 +3721,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="1">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D10" s="1">
         <v>0</v>
@@ -3730,7 +3730,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="3">
         <f>IF((C10-D10)&lt;0,0,C10-D10)</f>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H10" s="4">
         <f>IF((D10-C10)&lt;0,0,D10-C10)</f>
@@ -3745,7 +3745,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="1">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
@@ -3754,7 +3754,7 @@
       <c r="F11" s="5"/>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H11" s="4">
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
@@ -3769,7 +3769,7 @@
         <v>13</v>
       </c>
       <c r="C12" s="1">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D12" s="1">
         <v>0</v>
@@ -3778,7 +3778,7 @@
       <c r="F12" s="5"/>
       <c r="G12" s="3">
         <f>IF((C12-D12)&lt;0,0,C12-D12)</f>
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H12" s="4">
         <f>IF((D12-C12)&lt;0,0,D12-C12)</f>
@@ -3798,7 +3798,7 @@
         <v>8</v>
       </c>
       <c r="C14" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
@@ -3807,7 +3807,7 @@
       <c r="F14" s="5"/>
       <c r="G14" s="3">
         <f t="shared" ref="G14:G19" si="2">IF((C14-D14)&lt;0,0,C14-D14)</f>
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" ref="H14:H19" si="3">IF((D14-C14)&lt;0,0,D14-C14)</f>
@@ -3822,7 +3822,7 @@
         <v>10</v>
       </c>
       <c r="C15" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D15" s="1">
         <v>0</v>
@@ -3831,7 +3831,7 @@
       <c r="F15" s="5"/>
       <c r="G15" s="3">
         <f t="shared" si="2"/>
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H15" s="4">
         <f t="shared" si="3"/>
@@ -3846,7 +3846,7 @@
         <v>11</v>
       </c>
       <c r="C16" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D16" s="1">
         <v>0</v>
@@ -3855,7 +3855,7 @@
       <c r="F16" s="5"/>
       <c r="G16" s="3">
         <f t="shared" si="2"/>
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H16" s="4">
         <f t="shared" si="3"/>
@@ -3870,7 +3870,7 @@
         <v>14</v>
       </c>
       <c r="C17" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D17" s="1">
         <v>0</v>
@@ -3879,7 +3879,7 @@
       <c r="F17" s="5"/>
       <c r="G17" s="3">
         <f t="shared" si="2"/>
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H17" s="4">
         <f t="shared" si="3"/>
@@ -3894,7 +3894,7 @@
         <v>12</v>
       </c>
       <c r="C18" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D18" s="1">
         <v>0</v>
@@ -3903,7 +3903,7 @@
       <c r="F18" s="5"/>
       <c r="G18" s="3">
         <f t="shared" si="2"/>
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H18" s="4">
         <f t="shared" si="3"/>
@@ -3918,7 +3918,7 @@
         <v>13</v>
       </c>
       <c r="C19" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D19" s="1">
         <v>0</v>
@@ -3927,7 +3927,7 @@
       <c r="F19" s="5"/>
       <c r="G19" s="3">
         <f t="shared" si="2"/>
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H19" s="4">
         <f t="shared" si="3"/>
@@ -4192,7 +4192,7 @@
         <v>15</v>
       </c>
       <c r="C31" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D31" s="1">
         <v>200</v>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="27.75" customHeight="1">
@@ -4218,7 +4218,7 @@
         <v>16</v>
       </c>
       <c r="C32" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D32" s="1">
         <v>0</v>
@@ -4227,7 +4227,7 @@
       <c r="F32" s="5"/>
       <c r="G32" s="3">
         <f t="shared" si="6"/>
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="7"/>
@@ -4242,7 +4242,7 @@
         <v>13</v>
       </c>
       <c r="C33" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D33" s="1">
         <v>0</v>
@@ -4251,7 +4251,7 @@
       <c r="F33" s="5"/>
       <c r="G33" s="3">
         <f t="shared" si="6"/>
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H33" s="4">
         <f t="shared" si="7"/>
@@ -4266,7 +4266,7 @@
         <v>11</v>
       </c>
       <c r="C34" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D34" s="1">
         <v>0</v>
@@ -4275,7 +4275,7 @@
       <c r="F34" s="5"/>
       <c r="G34" s="3">
         <f t="shared" si="6"/>
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H34" s="4">
         <f t="shared" si="7"/>
@@ -4290,7 +4290,7 @@
         <v>17</v>
       </c>
       <c r="C35" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D35" s="1">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       <c r="F35" s="5"/>
       <c r="G35" s="3">
         <f t="shared" si="6"/>
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="7"/>
@@ -4314,7 +4314,7 @@
         <v>14</v>
       </c>
       <c r="C36" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D36" s="1">
         <v>200</v>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="H36" s="4">
         <f t="shared" si="7"/>
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="27.75" customHeight="1">
@@ -4340,7 +4340,7 @@
         <v>18</v>
       </c>
       <c r="C37" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D37" s="1">
         <v>200</v>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="H37" s="4">
         <f t="shared" si="7"/>
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="27.75" customHeight="1">
@@ -4366,7 +4366,7 @@
         <v>19</v>
       </c>
       <c r="C38" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D38" s="1">
         <v>0</v>
@@ -4375,7 +4375,7 @@
       <c r="F38" s="5"/>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
@@ -4390,7 +4390,7 @@
         <v>20</v>
       </c>
       <c r="C39" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D39" s="1">
         <v>0</v>
@@ -4399,7 +4399,7 @@
       <c r="F39" s="5"/>
       <c r="G39" s="3">
         <f t="shared" si="6"/>
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="7"/>
@@ -5745,8 +5745,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -5761,7 +5761,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -6002,18 +6002,18 @@
         <v>8</v>
       </c>
       <c r="C5" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D5" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="1"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5">
         <f t="shared" ref="H5:H77" si="2">IF((D5-E5)&lt;0,0,(D5-E5))</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I77" si="3">IF((E5-D5)&lt;0,0,(E5-D5))</f>
@@ -6021,14 +6021,14 @@
       </c>
       <c r="J5" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="1"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5">
         <f t="shared" ref="N5" si="4">IF((J5-K5)&lt;0,0,(J5-K5))</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="O5" s="5">
         <f t="shared" ref="O5" si="5">IF((K5-J5)&lt;0,0,(K5-J5))</f>
@@ -6036,14 +6036,14 @@
       </c>
       <c r="P5" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="Q5" s="5"/>
       <c r="R5" s="1"/>
       <c r="S5" s="5"/>
       <c r="T5" s="5">
         <f t="shared" ref="T5" si="6">IF((P5-Q5)&lt;0,0,(P5-Q5))</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" ref="U5" si="7">IF((Q5-P5)&lt;0,0,(Q5-P5))</f>
@@ -6051,14 +6051,14 @@
       </c>
       <c r="V5" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="W5" s="5"/>
       <c r="X5" s="1"/>
       <c r="Y5" s="5"/>
       <c r="Z5" s="5">
         <f t="shared" ref="Z5" si="8">IF((V5-W5)&lt;0,0,(V5-W5))</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="AA5" s="5">
         <f t="shared" ref="AA5" si="9">IF((W5-V5)&lt;0,0,(W5-V5))</f>
@@ -6073,18 +6073,18 @@
         <v>10</v>
       </c>
       <c r="C6" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D6" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="1"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5">
         <f t="shared" si="2"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="3"/>
@@ -6092,14 +6092,14 @@
       </c>
       <c r="J6" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="1"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5">
         <f t="shared" ref="N6:N69" si="10">IF((J6-K6)&lt;0,0,(J6-K6))</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="O6" s="5">
         <f t="shared" ref="O6:O69" si="11">IF((K6-J6)&lt;0,0,(K6-J6))</f>
@@ -6107,14 +6107,14 @@
       </c>
       <c r="P6" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="Q6" s="5"/>
       <c r="R6" s="1"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5">
         <f t="shared" ref="T6:T69" si="12">IF((P6-Q6)&lt;0,0,(P6-Q6))</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" ref="U6:U69" si="13">IF((Q6-P6)&lt;0,0,(Q6-P6))</f>
@@ -6122,14 +6122,14 @@
       </c>
       <c r="V6" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="W6" s="5"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="5"/>
       <c r="Z6" s="5">
         <f t="shared" ref="Z6:Z69" si="14">IF((V6-W6)&lt;0,0,(V6-W6))</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="AA6" s="5">
         <f t="shared" ref="AA6:AA69" si="15">IF((W6-V6)&lt;0,0,(W6-V6))</f>
@@ -6144,18 +6144,18 @@
         <v>11</v>
       </c>
       <c r="C7" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D7" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="1"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5">
         <f t="shared" si="2"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="3"/>
@@ -6163,14 +6163,14 @@
       </c>
       <c r="J7" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="K7" s="5"/>
       <c r="L7" s="1"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5">
         <f t="shared" si="10"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="O7" s="5">
         <f t="shared" si="11"/>
@@ -6178,14 +6178,14 @@
       </c>
       <c r="P7" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="Q7" s="5"/>
       <c r="R7" s="1"/>
       <c r="S7" s="5"/>
       <c r="T7" s="5">
         <f t="shared" si="12"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="13"/>
@@ -6193,14 +6193,14 @@
       </c>
       <c r="V7" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="W7" s="5"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="5"/>
       <c r="Z7" s="5">
         <f t="shared" si="14"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="AA7" s="5">
         <f t="shared" si="15"/>
@@ -6215,18 +6215,18 @@
         <v>12</v>
       </c>
       <c r="C8" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D8" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="1"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5">
         <f t="shared" si="2"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="3"/>
@@ -6234,14 +6234,14 @@
       </c>
       <c r="J8" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="1"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5">
         <f t="shared" si="10"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="O8" s="5">
         <f t="shared" si="11"/>
@@ -6249,14 +6249,14 @@
       </c>
       <c r="P8" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="Q8" s="5"/>
       <c r="R8" s="1"/>
       <c r="S8" s="5"/>
       <c r="T8" s="5">
         <f t="shared" si="12"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="13"/>
@@ -6264,14 +6264,14 @@
       </c>
       <c r="V8" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="W8" s="5"/>
       <c r="X8" s="1"/>
       <c r="Y8" s="5"/>
       <c r="Z8" s="5">
         <f t="shared" si="14"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="AA8" s="5">
         <f t="shared" si="15"/>
@@ -6286,18 +6286,18 @@
         <v>13</v>
       </c>
       <c r="C9" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D9" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="1"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5">
         <f t="shared" si="2"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="3"/>
@@ -6305,14 +6305,14 @@
       </c>
       <c r="J9" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="K9" s="5"/>
       <c r="L9" s="1"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5">
         <f t="shared" si="10"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="O9" s="5">
         <f t="shared" si="11"/>
@@ -6320,14 +6320,14 @@
       </c>
       <c r="P9" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="Q9" s="5"/>
       <c r="R9" s="1"/>
       <c r="S9" s="5"/>
       <c r="T9" s="5">
         <f t="shared" si="12"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="13"/>
@@ -6335,14 +6335,14 @@
       </c>
       <c r="V9" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="W9" s="5"/>
       <c r="X9" s="1"/>
       <c r="Y9" s="5"/>
       <c r="Z9" s="5">
         <f t="shared" si="14"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="AA9" s="5">
         <f t="shared" si="15"/>
@@ -6357,18 +6357,18 @@
         <v>15</v>
       </c>
       <c r="C10" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D10" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="1"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5">
         <f>IF((D10-E10)&lt;0,0,(D10-E10))</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="I10" s="5">
         <f>IF((E10-D10)&lt;0,0,(E10-D10))</f>
@@ -6376,14 +6376,14 @@
       </c>
       <c r="J10" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="1"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5">
         <f t="shared" si="10"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="O10" s="5">
         <f t="shared" si="11"/>
@@ -6391,14 +6391,14 @@
       </c>
       <c r="P10" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="Q10" s="5"/>
       <c r="R10" s="1"/>
       <c r="S10" s="5"/>
       <c r="T10" s="5">
         <f t="shared" si="12"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="13"/>
@@ -6406,14 +6406,14 @@
       </c>
       <c r="V10" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="W10" s="5"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="5"/>
       <c r="Z10" s="5">
         <f t="shared" si="14"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="AA10" s="5">
         <f t="shared" si="15"/>
@@ -6428,18 +6428,18 @@
         <v>16</v>
       </c>
       <c r="C11" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D11" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="1"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5">
         <f>IF((D11-E11)&lt;0,0,(D11-E11))</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="I11" s="5">
         <f>IF((E11-D11)&lt;0,0,(E11-D11))</f>
@@ -6447,14 +6447,14 @@
       </c>
       <c r="J11" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="K11" s="5"/>
       <c r="L11" s="1"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5">
         <f t="shared" si="10"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="O11" s="5">
         <f t="shared" si="11"/>
@@ -6462,14 +6462,14 @@
       </c>
       <c r="P11" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="Q11" s="5"/>
       <c r="R11" s="1"/>
       <c r="S11" s="5"/>
       <c r="T11" s="5">
         <f t="shared" si="12"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="13"/>
@@ -6477,14 +6477,14 @@
       </c>
       <c r="V11" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="W11" s="5"/>
       <c r="X11" s="1"/>
       <c r="Y11" s="5"/>
       <c r="Z11" s="5">
         <f t="shared" si="14"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="AA11" s="5">
         <f t="shared" si="15"/>
@@ -6499,18 +6499,18 @@
         <v>62</v>
       </c>
       <c r="C12" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D12" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="1"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5">
         <f>IF((D12-E12)&lt;0,0,(D12-E12))</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="I12" s="5">
         <f>IF((E12-D12)&lt;0,0,(E12-D12))</f>
@@ -6518,14 +6518,14 @@
       </c>
       <c r="J12" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="1"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5">
         <f t="shared" si="10"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="O12" s="5">
         <f t="shared" si="11"/>
@@ -6533,14 +6533,14 @@
       </c>
       <c r="P12" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="Q12" s="5"/>
       <c r="R12" s="1"/>
       <c r="S12" s="5"/>
       <c r="T12" s="5">
         <f t="shared" si="12"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="U12" s="5">
         <f t="shared" si="13"/>
@@ -6548,21 +6548,21 @@
       </c>
       <c r="V12" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="W12" s="5"/>
       <c r="X12" s="1"/>
       <c r="Y12" s="5"/>
       <c r="Z12" s="5">
         <f t="shared" si="14"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="AA12" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6583,18 +6583,18 @@
         <v>8</v>
       </c>
       <c r="C14" s="1">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D14" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="1"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5">
         <f t="shared" si="2"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="3"/>
@@ -6602,14 +6602,14 @@
       </c>
       <c r="J14" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="K14" s="5"/>
       <c r="L14" s="1"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5">
         <f t="shared" si="10"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="O14" s="5">
         <f t="shared" si="11"/>
@@ -6617,14 +6617,14 @@
       </c>
       <c r="P14" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="Q14" s="5"/>
       <c r="R14" s="1"/>
       <c r="S14" s="5"/>
       <c r="T14" s="5">
         <f t="shared" si="12"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="U14" s="5">
         <f t="shared" si="13"/>
@@ -6632,14 +6632,14 @@
       </c>
       <c r="V14" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="W14" s="5"/>
       <c r="X14" s="1"/>
       <c r="Y14" s="5"/>
       <c r="Z14" s="5">
         <f t="shared" si="14"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="AA14" s="5">
         <f t="shared" si="15"/>
@@ -6654,18 +6654,18 @@
         <v>10</v>
       </c>
       <c r="C15" s="1">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D15" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="1"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5">
         <f t="shared" si="2"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="3"/>
@@ -6673,14 +6673,14 @@
       </c>
       <c r="J15" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="K15" s="5"/>
       <c r="L15" s="1"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5">
         <f t="shared" si="10"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="O15" s="5">
         <f t="shared" si="11"/>
@@ -6688,14 +6688,14 @@
       </c>
       <c r="P15" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="Q15" s="5"/>
       <c r="R15" s="1"/>
       <c r="S15" s="5"/>
       <c r="T15" s="5">
         <f t="shared" si="12"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="U15" s="5">
         <f t="shared" si="13"/>
@@ -6703,14 +6703,14 @@
       </c>
       <c r="V15" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="W15" s="5"/>
       <c r="X15" s="1"/>
       <c r="Y15" s="5"/>
       <c r="Z15" s="5">
         <f t="shared" si="14"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="AA15" s="5">
         <f t="shared" si="15"/>
@@ -6725,11 +6725,11 @@
         <v>11</v>
       </c>
       <c r="C16" s="1">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D16" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="E16" s="5">
         <v>158</v>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="H16" s="5">
         <f t="shared" si="2"/>
-        <v>1346</v>
+        <v>1354</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" si="3"/>
@@ -6750,14 +6750,14 @@
       </c>
       <c r="J16" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="K16" s="5"/>
       <c r="L16" s="1"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5">
         <f t="shared" si="10"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="O16" s="5">
         <f t="shared" si="11"/>
@@ -6765,14 +6765,14 @@
       </c>
       <c r="P16" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="Q16" s="5"/>
       <c r="R16" s="1"/>
       <c r="S16" s="5"/>
       <c r="T16" s="5">
         <f t="shared" si="12"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="U16" s="5">
         <f t="shared" si="13"/>
@@ -6780,14 +6780,14 @@
       </c>
       <c r="V16" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="W16" s="5"/>
       <c r="X16" s="1"/>
       <c r="Y16" s="5"/>
       <c r="Z16" s="5">
         <f t="shared" si="14"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="AA16" s="5">
         <f t="shared" si="15"/>
@@ -6802,11 +6802,11 @@
         <v>12</v>
       </c>
       <c r="C17" s="1">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="E17" s="5">
         <v>158</v>
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H17" s="5">
         <f t="shared" si="2"/>
-        <v>1346</v>
+        <v>1354</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="3"/>
@@ -6827,14 +6827,14 @@
       </c>
       <c r="J17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="K17" s="5"/>
       <c r="L17" s="1"/>
       <c r="M17" s="5"/>
       <c r="N17" s="5">
         <f t="shared" si="10"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="O17" s="5">
         <f t="shared" si="11"/>
@@ -6842,14 +6842,14 @@
       </c>
       <c r="P17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="Q17" s="5"/>
       <c r="R17" s="1"/>
       <c r="S17" s="5"/>
       <c r="T17" s="5">
         <f t="shared" si="12"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="U17" s="5">
         <f t="shared" si="13"/>
@@ -6857,14 +6857,14 @@
       </c>
       <c r="V17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="W17" s="5"/>
       <c r="X17" s="1"/>
       <c r="Y17" s="5"/>
       <c r="Z17" s="5">
         <f t="shared" si="14"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" si="15"/>
@@ -6879,18 +6879,18 @@
         <v>13</v>
       </c>
       <c r="C18" s="1">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D18" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="1"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5">
         <f t="shared" si="2"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="3"/>
@@ -6898,14 +6898,14 @@
       </c>
       <c r="J18" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="K18" s="5"/>
       <c r="L18" s="1"/>
       <c r="M18" s="5"/>
       <c r="N18" s="5">
         <f t="shared" si="10"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="O18" s="5">
         <f t="shared" si="11"/>
@@ -6913,14 +6913,14 @@
       </c>
       <c r="P18" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="Q18" s="5"/>
       <c r="R18" s="1"/>
       <c r="S18" s="5"/>
       <c r="T18" s="5">
         <f t="shared" si="12"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="U18" s="5">
         <f t="shared" si="13"/>
@@ -6928,14 +6928,14 @@
       </c>
       <c r="V18" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="W18" s="5"/>
       <c r="X18" s="1"/>
       <c r="Y18" s="5"/>
       <c r="Z18" s="5">
         <f t="shared" si="14"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="AA18" s="5">
         <f t="shared" si="15"/>
@@ -6950,11 +6950,11 @@
         <v>16</v>
       </c>
       <c r="C19" s="1">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="E19" s="5">
         <v>158</v>
@@ -6967,7 +6967,7 @@
       </c>
       <c r="H19" s="5">
         <f>IF((D19-E19)&lt;0,0,(D19-E19))</f>
-        <v>1346</v>
+        <v>1354</v>
       </c>
       <c r="I19" s="5">
         <f>IF((E19-D19)&lt;0,0,(E19-D19))</f>
@@ -6975,14 +6975,14 @@
       </c>
       <c r="J19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="K19" s="5"/>
       <c r="L19" s="1"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5">
         <f t="shared" si="10"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="O19" s="5">
         <f t="shared" si="11"/>
@@ -6990,14 +6990,14 @@
       </c>
       <c r="P19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="Q19" s="5"/>
       <c r="R19" s="1"/>
       <c r="S19" s="5"/>
       <c r="T19" s="5">
         <f t="shared" si="12"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="U19" s="5">
         <f t="shared" si="13"/>
@@ -7005,14 +7005,14 @@
       </c>
       <c r="V19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="W19" s="5"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="5"/>
       <c r="Z19" s="5">
         <f t="shared" si="14"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="AA19" s="5">
         <f t="shared" si="15"/>
@@ -7027,11 +7027,11 @@
         <v>15</v>
       </c>
       <c r="C20" s="1">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D20" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="E20" s="5">
         <v>158</v>
@@ -7044,7 +7044,7 @@
       </c>
       <c r="H20" s="5">
         <f>IF((D20-E20)&lt;0,0,(D20-E20))</f>
-        <v>1346</v>
+        <v>1354</v>
       </c>
       <c r="I20" s="5">
         <f>IF((E20-D20)&lt;0,0,(E20-D20))</f>
@@ -7052,14 +7052,14 @@
       </c>
       <c r="J20" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="K20" s="5"/>
       <c r="L20" s="1"/>
       <c r="M20" s="5"/>
       <c r="N20" s="5">
         <f t="shared" si="10"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="O20" s="5">
         <f t="shared" si="11"/>
@@ -7067,14 +7067,14 @@
       </c>
       <c r="P20" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="Q20" s="5"/>
       <c r="R20" s="1"/>
       <c r="S20" s="5"/>
       <c r="T20" s="5">
         <f t="shared" si="12"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="U20" s="5">
         <f t="shared" si="13"/>
@@ -7082,14 +7082,14 @@
       </c>
       <c r="V20" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="W20" s="5"/>
       <c r="X20" s="1"/>
       <c r="Y20" s="5"/>
       <c r="Z20" s="5">
         <f t="shared" si="14"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="AA20" s="5">
         <f t="shared" si="15"/>
@@ -7104,18 +7104,18 @@
         <v>62</v>
       </c>
       <c r="C21" s="1">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D21" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="1"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5">
         <f>IF((D21-E21)&lt;0,0,(D21-E21))</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="I21" s="5">
         <f>IF((E21-D21)&lt;0,0,(E21-D21))</f>
@@ -7123,14 +7123,14 @@
       </c>
       <c r="J21" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="K21" s="5"/>
       <c r="L21" s="1"/>
       <c r="M21" s="5"/>
       <c r="N21" s="5">
         <f t="shared" si="10"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="O21" s="5">
         <f t="shared" si="11"/>
@@ -7138,14 +7138,14 @@
       </c>
       <c r="P21" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="Q21" s="5"/>
       <c r="R21" s="1"/>
       <c r="S21" s="5"/>
       <c r="T21" s="5">
         <f t="shared" si="12"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="U21" s="5">
         <f t="shared" si="13"/>
@@ -7153,21 +7153,21 @@
       </c>
       <c r="V21" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="W21" s="5"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="5"/>
       <c r="Z21" s="5">
         <f t="shared" si="14"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="AA21" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -7189,18 +7189,18 @@
         <v>8</v>
       </c>
       <c r="C23" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D23" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="1"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5">
         <f t="shared" si="2"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="3"/>
@@ -7208,14 +7208,14 @@
       </c>
       <c r="J23" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="K23" s="5"/>
       <c r="L23" s="1"/>
       <c r="M23" s="5"/>
       <c r="N23" s="5">
         <f t="shared" si="10"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="O23" s="5">
         <f t="shared" si="11"/>
@@ -7223,14 +7223,14 @@
       </c>
       <c r="P23" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="Q23" s="5"/>
       <c r="R23" s="1"/>
       <c r="S23" s="5"/>
       <c r="T23" s="5">
         <f t="shared" si="12"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="U23" s="5">
         <f t="shared" si="13"/>
@@ -7238,14 +7238,14 @@
       </c>
       <c r="V23" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="W23" s="5"/>
       <c r="X23" s="1"/>
       <c r="Y23" s="5"/>
       <c r="Z23" s="5">
         <f t="shared" si="14"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="AA23" s="5">
         <f t="shared" si="15"/>
@@ -7260,18 +7260,18 @@
         <v>10</v>
       </c>
       <c r="C24" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D24" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="1"/>
       <c r="G24" s="5"/>
       <c r="H24" s="5">
         <f t="shared" si="2"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="3"/>
@@ -7279,14 +7279,14 @@
       </c>
       <c r="J24" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="K24" s="5"/>
       <c r="L24" s="1"/>
       <c r="M24" s="5"/>
       <c r="N24" s="5">
         <f t="shared" si="10"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="O24" s="5">
         <f t="shared" si="11"/>
@@ -7294,14 +7294,14 @@
       </c>
       <c r="P24" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="Q24" s="5"/>
       <c r="R24" s="1"/>
       <c r="S24" s="5"/>
       <c r="T24" s="5">
         <f t="shared" si="12"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="U24" s="5">
         <f t="shared" si="13"/>
@@ -7309,14 +7309,14 @@
       </c>
       <c r="V24" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="W24" s="5"/>
       <c r="X24" s="1"/>
       <c r="Y24" s="5"/>
       <c r="Z24" s="5">
         <f t="shared" si="14"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="AA24" s="5">
         <f t="shared" si="15"/>
@@ -7331,11 +7331,11 @@
         <v>11</v>
       </c>
       <c r="C25" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D25" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="E25" s="5">
         <v>105</v>
@@ -7344,7 +7344,7 @@
       <c r="G25" s="5"/>
       <c r="H25" s="5">
         <f t="shared" si="2"/>
-        <v>1151</v>
+        <v>1143</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="3"/>
@@ -7352,14 +7352,14 @@
       </c>
       <c r="J25" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="K25" s="5"/>
       <c r="L25" s="1"/>
       <c r="M25" s="5"/>
       <c r="N25" s="5">
         <f t="shared" si="10"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="O25" s="5">
         <f t="shared" si="11"/>
@@ -7367,14 +7367,14 @@
       </c>
       <c r="P25" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="Q25" s="5"/>
       <c r="R25" s="1"/>
       <c r="S25" s="5"/>
       <c r="T25" s="5">
         <f t="shared" si="12"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="U25" s="5">
         <f t="shared" si="13"/>
@@ -7382,14 +7382,14 @@
       </c>
       <c r="V25" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="W25" s="5"/>
       <c r="X25" s="1"/>
       <c r="Y25" s="5"/>
       <c r="Z25" s="5">
         <f t="shared" si="14"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="AA25" s="5">
         <f t="shared" si="15"/>
@@ -7404,11 +7404,11 @@
         <v>14</v>
       </c>
       <c r="C26" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D26" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="1">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="H26" s="5">
         <f t="shared" si="2"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="3"/>
@@ -7427,14 +7427,14 @@
       </c>
       <c r="J26" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="K26" s="5"/>
       <c r="L26" s="1"/>
       <c r="M26" s="5"/>
       <c r="N26" s="5">
         <f t="shared" si="10"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="O26" s="5">
         <f t="shared" si="11"/>
@@ -7442,14 +7442,14 @@
       </c>
       <c r="P26" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="Q26" s="5"/>
       <c r="R26" s="1"/>
       <c r="S26" s="5"/>
       <c r="T26" s="5">
         <f t="shared" si="12"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="U26" s="5">
         <f t="shared" si="13"/>
@@ -7457,14 +7457,14 @@
       </c>
       <c r="V26" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="W26" s="5"/>
       <c r="X26" s="1"/>
       <c r="Y26" s="5"/>
       <c r="Z26" s="5">
         <f t="shared" si="14"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="AA26" s="5">
         <f t="shared" si="15"/>
@@ -7479,11 +7479,11 @@
         <v>12</v>
       </c>
       <c r="C27" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D27" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="1">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="H27" s="5">
         <f t="shared" si="2"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="3"/>
@@ -7502,14 +7502,14 @@
       </c>
       <c r="J27" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="K27" s="5"/>
       <c r="L27" s="1"/>
       <c r="M27" s="5"/>
       <c r="N27" s="5">
         <f t="shared" si="10"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="O27" s="5">
         <f t="shared" si="11"/>
@@ -7517,14 +7517,14 @@
       </c>
       <c r="P27" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="Q27" s="5"/>
       <c r="R27" s="1"/>
       <c r="S27" s="5"/>
       <c r="T27" s="5">
         <f t="shared" si="12"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="U27" s="5">
         <f t="shared" si="13"/>
@@ -7532,14 +7532,14 @@
       </c>
       <c r="V27" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="W27" s="5"/>
       <c r="X27" s="1"/>
       <c r="Y27" s="5"/>
       <c r="Z27" s="5">
         <f t="shared" si="14"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="AA27" s="5">
         <f t="shared" si="15"/>
@@ -7554,11 +7554,11 @@
         <v>13</v>
       </c>
       <c r="C28" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D28" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="1">
@@ -7569,7 +7569,7 @@
       </c>
       <c r="H28" s="5">
         <f t="shared" si="2"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="3"/>
@@ -7577,14 +7577,14 @@
       </c>
       <c r="J28" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="K28" s="5"/>
       <c r="L28" s="1"/>
       <c r="M28" s="5"/>
       <c r="N28" s="5">
         <f t="shared" si="10"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="O28" s="5">
         <f t="shared" si="11"/>
@@ -7592,14 +7592,14 @@
       </c>
       <c r="P28" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="Q28" s="5"/>
       <c r="R28" s="1"/>
       <c r="S28" s="5"/>
       <c r="T28" s="5">
         <f t="shared" si="12"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="U28" s="5">
         <f t="shared" si="13"/>
@@ -7607,14 +7607,14 @@
       </c>
       <c r="V28" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="W28" s="5"/>
       <c r="X28" s="1"/>
       <c r="Y28" s="5"/>
       <c r="Z28" s="5">
         <f t="shared" si="14"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="AA28" s="5">
         <f t="shared" si="15"/>
@@ -7629,11 +7629,11 @@
         <v>15</v>
       </c>
       <c r="C29" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D29" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="1">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="H29" s="5">
         <f>IF((D29-E29)&lt;0,0,(D29-E29))</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="I29" s="5">
         <f>IF((E29-D29)&lt;0,0,(E29-D29))</f>
@@ -7652,14 +7652,14 @@
       </c>
       <c r="J29" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="K29" s="5"/>
       <c r="L29" s="1"/>
       <c r="M29" s="5"/>
       <c r="N29" s="5">
         <f t="shared" si="10"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="O29" s="5">
         <f t="shared" si="11"/>
@@ -7667,14 +7667,14 @@
       </c>
       <c r="P29" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="Q29" s="5"/>
       <c r="R29" s="1"/>
       <c r="S29" s="5"/>
       <c r="T29" s="5">
         <f t="shared" si="12"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="U29" s="5">
         <f t="shared" si="13"/>
@@ -7682,14 +7682,14 @@
       </c>
       <c r="V29" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="W29" s="5"/>
       <c r="X29" s="1"/>
       <c r="Y29" s="5"/>
       <c r="Z29" s="5">
         <f t="shared" si="14"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="AA29" s="5">
         <f t="shared" si="15"/>
@@ -7704,11 +7704,11 @@
         <v>16</v>
       </c>
       <c r="C30" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D30" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="E30" s="5">
         <v>105</v>
@@ -7721,7 +7721,7 @@
       </c>
       <c r="H30" s="5">
         <f>IF((D30-E30)&lt;0,0,(D30-E30))</f>
-        <v>1151</v>
+        <v>1143</v>
       </c>
       <c r="I30" s="5">
         <f>IF((E30-D30)&lt;0,0,(E30-D30))</f>
@@ -7729,14 +7729,14 @@
       </c>
       <c r="J30" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="K30" s="5"/>
       <c r="L30" s="1"/>
       <c r="M30" s="5"/>
       <c r="N30" s="5">
         <f t="shared" si="10"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="O30" s="5">
         <f t="shared" si="11"/>
@@ -7744,14 +7744,14 @@
       </c>
       <c r="P30" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="Q30" s="5"/>
       <c r="R30" s="1"/>
       <c r="S30" s="5"/>
       <c r="T30" s="5">
         <f t="shared" si="12"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="U30" s="5">
         <f t="shared" si="13"/>
@@ -7759,14 +7759,14 @@
       </c>
       <c r="V30" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="W30" s="5"/>
       <c r="X30" s="1"/>
       <c r="Y30" s="5"/>
       <c r="Z30" s="5">
         <f t="shared" si="14"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="AA30" s="5">
         <f t="shared" si="15"/>
@@ -7781,18 +7781,18 @@
         <v>62</v>
       </c>
       <c r="C31" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D31" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="1"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5">
         <f>IF((D31-E31)&lt;0,0,(D31-E31))</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="I31" s="5">
         <f>IF((E31-D31)&lt;0,0,(E31-D31))</f>
@@ -7800,14 +7800,14 @@
       </c>
       <c r="J31" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="K31" s="5"/>
       <c r="L31" s="1"/>
       <c r="M31" s="5"/>
       <c r="N31" s="5">
         <f t="shared" si="10"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="O31" s="5">
         <f t="shared" si="11"/>
@@ -7815,14 +7815,14 @@
       </c>
       <c r="P31" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="Q31" s="5"/>
       <c r="R31" s="1"/>
       <c r="S31" s="5"/>
       <c r="T31" s="5">
         <f t="shared" si="12"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="U31" s="5">
         <f t="shared" si="13"/>
@@ -7830,14 +7830,14 @@
       </c>
       <c r="V31" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="W31" s="5"/>
       <c r="X31" s="1"/>
       <c r="Y31" s="5"/>
       <c r="Z31" s="5">
         <f t="shared" si="14"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="AA31" s="5">
         <f t="shared" si="15"/>
@@ -8519,11 +8519,11 @@
         <v>15</v>
       </c>
       <c r="C43" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="E43" s="44">
         <v>97</v>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H43" s="5">
         <f t="shared" si="2"/>
-        <v>1327</v>
+        <v>1311</v>
       </c>
       <c r="I43" s="5">
         <f t="shared" si="3"/>
@@ -8544,14 +8544,14 @@
       </c>
       <c r="J43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="K43" s="5"/>
       <c r="L43" s="1"/>
       <c r="M43" s="5"/>
       <c r="N43" s="5">
         <f t="shared" si="10"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="O43" s="5">
         <f t="shared" si="11"/>
@@ -8559,14 +8559,14 @@
       </c>
       <c r="P43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="Q43" s="5"/>
       <c r="R43" s="1"/>
       <c r="S43" s="5"/>
       <c r="T43" s="5">
         <f t="shared" si="12"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="U43" s="5">
         <f t="shared" si="13"/>
@@ -8574,14 +8574,14 @@
       </c>
       <c r="V43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="W43" s="5"/>
       <c r="X43" s="1"/>
       <c r="Y43" s="5"/>
       <c r="Z43" s="5">
         <f t="shared" si="14"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="AA43" s="5">
         <f t="shared" si="15"/>
@@ -8596,11 +8596,11 @@
         <v>16</v>
       </c>
       <c r="C44" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D44" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="E44" s="44">
         <v>97</v>
@@ -8613,7 +8613,7 @@
       </c>
       <c r="H44" s="5">
         <f t="shared" si="2"/>
-        <v>1327</v>
+        <v>1311</v>
       </c>
       <c r="I44" s="5">
         <f t="shared" si="3"/>
@@ -8621,14 +8621,14 @@
       </c>
       <c r="J44" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="K44" s="5"/>
       <c r="L44" s="1"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5">
         <f t="shared" si="10"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="O44" s="5">
         <f t="shared" si="11"/>
@@ -8636,14 +8636,14 @@
       </c>
       <c r="P44" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="Q44" s="5"/>
       <c r="R44" s="1"/>
       <c r="S44" s="5"/>
       <c r="T44" s="5">
         <f t="shared" si="12"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="U44" s="5">
         <f t="shared" si="13"/>
@@ -8651,14 +8651,14 @@
       </c>
       <c r="V44" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="W44" s="5"/>
       <c r="X44" s="1"/>
       <c r="Y44" s="5"/>
       <c r="Z44" s="5">
         <f t="shared" si="14"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="AA44" s="5">
         <f t="shared" si="15"/>
@@ -8673,11 +8673,11 @@
         <v>13</v>
       </c>
       <c r="C45" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="E45" s="44">
         <v>97</v>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="H45" s="5">
         <f t="shared" si="2"/>
-        <v>1327</v>
+        <v>1311</v>
       </c>
       <c r="I45" s="5">
         <f t="shared" si="3"/>
@@ -8698,14 +8698,14 @@
       </c>
       <c r="J45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="K45" s="5"/>
       <c r="L45" s="1"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5">
         <f t="shared" si="10"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="O45" s="5">
         <f t="shared" si="11"/>
@@ -8713,14 +8713,14 @@
       </c>
       <c r="P45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="Q45" s="5"/>
       <c r="R45" s="1"/>
       <c r="S45" s="5"/>
       <c r="T45" s="5">
         <f t="shared" si="12"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="U45" s="5">
         <f t="shared" si="13"/>
@@ -8728,14 +8728,14 @@
       </c>
       <c r="V45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="W45" s="5"/>
       <c r="X45" s="1"/>
       <c r="Y45" s="5"/>
       <c r="Z45" s="5">
         <f t="shared" si="14"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="AA45" s="5">
         <f t="shared" si="15"/>
@@ -8750,11 +8750,11 @@
         <v>11</v>
       </c>
       <c r="C46" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D46" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="E46" s="44">
         <v>97</v>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="H46" s="5">
         <f t="shared" si="2"/>
-        <v>1327</v>
+        <v>1311</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" si="3"/>
@@ -8775,14 +8775,14 @@
       </c>
       <c r="J46" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="K46" s="5"/>
       <c r="L46" s="1"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5">
         <f t="shared" si="10"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="O46" s="5">
         <f t="shared" si="11"/>
@@ -8790,14 +8790,14 @@
       </c>
       <c r="P46" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="Q46" s="5"/>
       <c r="R46" s="1"/>
       <c r="S46" s="5"/>
       <c r="T46" s="5">
         <f t="shared" si="12"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="U46" s="5">
         <f t="shared" si="13"/>
@@ -8805,14 +8805,14 @@
       </c>
       <c r="V46" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="W46" s="5"/>
       <c r="X46" s="1"/>
       <c r="Y46" s="5"/>
       <c r="Z46" s="5">
         <f t="shared" si="14"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="AA46" s="5">
         <f t="shared" si="15"/>
@@ -8827,11 +8827,11 @@
         <v>17</v>
       </c>
       <c r="C47" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D47" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="E47" s="44">
         <v>97</v>
@@ -8844,7 +8844,7 @@
       </c>
       <c r="H47" s="5">
         <f t="shared" si="2"/>
-        <v>1327</v>
+        <v>1311</v>
       </c>
       <c r="I47" s="5">
         <f t="shared" si="3"/>
@@ -8852,14 +8852,14 @@
       </c>
       <c r="J47" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="K47" s="5"/>
       <c r="L47" s="1"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5">
         <f t="shared" si="10"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="O47" s="5">
         <f t="shared" si="11"/>
@@ -8867,14 +8867,14 @@
       </c>
       <c r="P47" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="Q47" s="5"/>
       <c r="R47" s="1"/>
       <c r="S47" s="5"/>
       <c r="T47" s="5">
         <f t="shared" si="12"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="U47" s="5">
         <f t="shared" si="13"/>
@@ -8882,14 +8882,14 @@
       </c>
       <c r="V47" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="W47" s="5"/>
       <c r="X47" s="1"/>
       <c r="Y47" s="5"/>
       <c r="Z47" s="5">
         <f t="shared" si="14"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="AA47" s="5">
         <f t="shared" si="15"/>
@@ -8904,18 +8904,18 @@
         <v>14</v>
       </c>
       <c r="C48" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D48" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="E48" s="42"/>
       <c r="F48" s="1"/>
       <c r="G48" s="5"/>
       <c r="H48" s="5">
         <f t="shared" si="2"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="I48" s="5">
         <f t="shared" si="3"/>
@@ -8923,14 +8923,14 @@
       </c>
       <c r="J48" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="K48" s="5"/>
       <c r="L48" s="1"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5">
         <f t="shared" si="10"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="O48" s="5">
         <f t="shared" si="11"/>
@@ -8938,14 +8938,14 @@
       </c>
       <c r="P48" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="Q48" s="5"/>
       <c r="R48" s="1"/>
       <c r="S48" s="5"/>
       <c r="T48" s="5">
         <f t="shared" si="12"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="U48" s="5">
         <f t="shared" si="13"/>
@@ -8953,14 +8953,14 @@
       </c>
       <c r="V48" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="W48" s="5"/>
       <c r="X48" s="1"/>
       <c r="Y48" s="5"/>
       <c r="Z48" s="5">
         <f t="shared" si="14"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="AA48" s="5">
         <f t="shared" si="15"/>
@@ -8975,11 +8975,11 @@
         <v>18</v>
       </c>
       <c r="C49" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D49" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="E49" s="44">
         <v>97</v>
@@ -8992,7 +8992,7 @@
       </c>
       <c r="H49" s="5">
         <f t="shared" si="2"/>
-        <v>1327</v>
+        <v>1311</v>
       </c>
       <c r="I49" s="5">
         <f t="shared" si="3"/>
@@ -9000,14 +9000,14 @@
       </c>
       <c r="J49" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="K49" s="5"/>
       <c r="L49" s="1"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5">
         <f t="shared" si="10"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="O49" s="5">
         <f t="shared" si="11"/>
@@ -9015,14 +9015,14 @@
       </c>
       <c r="P49" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="Q49" s="5"/>
       <c r="R49" s="1"/>
       <c r="S49" s="5"/>
       <c r="T49" s="5">
         <f t="shared" si="12"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="U49" s="5">
         <f t="shared" si="13"/>
@@ -9030,14 +9030,14 @@
       </c>
       <c r="V49" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="W49" s="5"/>
       <c r="X49" s="1"/>
       <c r="Y49" s="5"/>
       <c r="Z49" s="5">
         <f t="shared" si="14"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="AA49" s="5">
         <f t="shared" si="15"/>
@@ -9052,11 +9052,11 @@
         <v>19</v>
       </c>
       <c r="C50" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D50" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="E50" s="44">
         <v>97</v>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="H50" s="5">
         <f t="shared" si="2"/>
-        <v>1327</v>
+        <v>1311</v>
       </c>
       <c r="I50" s="5">
         <f t="shared" si="3"/>
@@ -9077,14 +9077,14 @@
       </c>
       <c r="J50" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="K50" s="5"/>
       <c r="L50" s="1"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5">
         <f t="shared" si="10"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="O50" s="5">
         <f t="shared" si="11"/>
@@ -9092,14 +9092,14 @@
       </c>
       <c r="P50" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="Q50" s="5"/>
       <c r="R50" s="1"/>
       <c r="S50" s="5"/>
       <c r="T50" s="5">
         <f t="shared" si="12"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="U50" s="5">
         <f t="shared" si="13"/>
@@ -9107,14 +9107,14 @@
       </c>
       <c r="V50" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="W50" s="5"/>
       <c r="X50" s="1"/>
       <c r="Y50" s="5"/>
       <c r="Z50" s="5">
         <f t="shared" si="14"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="AA50" s="5">
         <f t="shared" si="15"/>
@@ -9129,11 +9129,11 @@
         <v>20</v>
       </c>
       <c r="C51" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D51" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="E51" s="44">
         <v>97</v>
@@ -9144,7 +9144,7 @@
       <c r="G51" s="5"/>
       <c r="H51" s="5">
         <f t="shared" si="2"/>
-        <v>1327</v>
+        <v>1311</v>
       </c>
       <c r="I51" s="5">
         <f t="shared" si="3"/>
@@ -9152,14 +9152,14 @@
       </c>
       <c r="J51" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="K51" s="5"/>
       <c r="L51" s="1"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5">
         <f t="shared" si="10"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="O51" s="5">
         <f t="shared" si="11"/>
@@ -9167,14 +9167,14 @@
       </c>
       <c r="P51" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="Q51" s="5"/>
       <c r="R51" s="1"/>
       <c r="S51" s="5"/>
       <c r="T51" s="5">
         <f t="shared" si="12"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="U51" s="5">
         <f t="shared" si="13"/>
@@ -9182,14 +9182,14 @@
       </c>
       <c r="V51" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="W51" s="5"/>
       <c r="X51" s="1"/>
       <c r="Y51" s="5"/>
       <c r="Z51" s="5">
         <f t="shared" si="14"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="AA51" s="5">
         <f t="shared" si="15"/>
@@ -13997,7 +13997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
+    <row r="127" spans="1:27" ht="19.5">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
@@ -14056,189 +14056,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C2:C3 C112:C127 C5:C12 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110" name="Textbooks"/>
+    <protectedRange sqref="C2:C3 C112:C127 C33:C41 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C5:C12 C14:C21 C23:C31 C43:C51" name="Textbooks"/>
     <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
     <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
   </protectedRanges>
@@ -14253,8 +14073,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
@@ -14272,7 +14092,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -14426,18 +14246,18 @@
         <v>8</v>
       </c>
       <c r="C3" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D3" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="1"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5">
         <f t="shared" ref="H3:H83" si="0">IF((D3-E3)&lt;0,0,(D3-E3))</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" ref="I3:I83" si="1">IF((E3-D3)&lt;0,0,(E3-D3))</f>
@@ -14445,14 +14265,14 @@
       </c>
       <c r="J3" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="K3" s="5"/>
       <c r="L3" s="1"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5">
         <f t="shared" ref="N3:N72" si="2">IF((J3-K3)&lt;0,0,(J3-K3))</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="O3" s="5">
         <f t="shared" ref="O3:O72" si="3">IF((K3-J3)&lt;0,0,(K3-J3))</f>
@@ -14460,14 +14280,14 @@
       </c>
       <c r="P3" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="Q3" s="5"/>
       <c r="R3" s="1"/>
       <c r="S3" s="5"/>
       <c r="T3" s="5">
         <f t="shared" ref="T3:T72" si="4">IF((P3-Q3)&lt;0,0,(P3-Q3))</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="U3" s="5">
         <f t="shared" ref="U3:U72" si="5">IF((Q3-P3)&lt;0,0,(Q3-P3))</f>
@@ -14475,14 +14295,14 @@
       </c>
       <c r="V3" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="W3" s="5"/>
       <c r="X3" s="1"/>
       <c r="Y3" s="5"/>
       <c r="Z3" s="5">
         <f t="shared" ref="Z3:Z72" si="6">IF((V3-W3)&lt;0,0,(V3-W3))</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="AA3" s="5">
         <f t="shared" ref="AA3:AA72" si="7">IF((W3-V3)&lt;0,0,(W3-V3))</f>
@@ -14497,18 +14317,18 @@
         <v>10</v>
       </c>
       <c r="C4" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D4" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="1"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5">
         <f t="shared" si="0"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="I4" s="5">
         <f t="shared" si="1"/>
@@ -14516,14 +14336,14 @@
       </c>
       <c r="J4" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="K4" s="5"/>
       <c r="L4" s="1"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5">
         <f t="shared" si="2"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="O4" s="5">
         <f t="shared" si="3"/>
@@ -14531,14 +14351,14 @@
       </c>
       <c r="P4" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="Q4" s="5"/>
       <c r="R4" s="1"/>
       <c r="S4" s="5"/>
       <c r="T4" s="5">
         <f t="shared" si="4"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" si="5"/>
@@ -14546,14 +14366,14 @@
       </c>
       <c r="V4" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="W4" s="5"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="5"/>
       <c r="Z4" s="5">
         <f t="shared" si="6"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="AA4" s="5">
         <f t="shared" si="7"/>
@@ -14568,18 +14388,18 @@
         <v>11</v>
       </c>
       <c r="C5" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D5" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="1"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5">
         <f t="shared" si="0"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" si="1"/>
@@ -14587,14 +14407,14 @@
       </c>
       <c r="J5" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="1"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5">
         <f t="shared" si="2"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="O5" s="5">
         <f t="shared" si="3"/>
@@ -14602,14 +14422,14 @@
       </c>
       <c r="P5" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="Q5" s="5"/>
       <c r="R5" s="1"/>
       <c r="S5" s="5"/>
       <c r="T5" s="5">
         <f t="shared" si="4"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="5"/>
@@ -14617,14 +14437,14 @@
       </c>
       <c r="V5" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="W5" s="5"/>
       <c r="X5" s="1"/>
       <c r="Y5" s="5"/>
       <c r="Z5" s="5">
         <f t="shared" si="6"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="AA5" s="5">
         <f t="shared" si="7"/>
@@ -14639,18 +14459,18 @@
         <v>12</v>
       </c>
       <c r="C6" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D6" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="1"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5">
         <f t="shared" si="0"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="1"/>
@@ -14658,14 +14478,14 @@
       </c>
       <c r="J6" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="1"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5">
         <f t="shared" si="2"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="O6" s="5">
         <f t="shared" si="3"/>
@@ -14673,14 +14493,14 @@
       </c>
       <c r="P6" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="Q6" s="5"/>
       <c r="R6" s="1"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5">
         <f t="shared" si="4"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="5"/>
@@ -14688,14 +14508,14 @@
       </c>
       <c r="V6" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="W6" s="5"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="5"/>
       <c r="Z6" s="5">
         <f t="shared" si="6"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="AA6" s="5">
         <f t="shared" si="7"/>
@@ -14710,11 +14530,11 @@
         <v>13</v>
       </c>
       <c r="C7" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D7" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="E7" s="5">
         <v>13</v>
@@ -14727,7 +14547,7 @@
       </c>
       <c r="H7" s="5">
         <f t="shared" si="0"/>
-        <v>1203</v>
+        <v>1219</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="1"/>
@@ -14735,14 +14555,14 @@
       </c>
       <c r="J7" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="K7" s="5"/>
       <c r="L7" s="1"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5">
         <f t="shared" si="2"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="O7" s="5">
         <f t="shared" si="3"/>
@@ -14750,7 +14570,7 @@
       </c>
       <c r="P7" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="Q7" s="5"/>
       <c r="R7" s="1">
@@ -14761,7 +14581,7 @@
       </c>
       <c r="T7" s="5">
         <f t="shared" si="4"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="5"/>
@@ -14769,14 +14589,14 @@
       </c>
       <c r="V7" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="W7" s="5"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="5"/>
       <c r="Z7" s="5">
         <f t="shared" si="6"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="AA7" s="5">
         <f t="shared" si="7"/>
@@ -14791,18 +14611,18 @@
         <v>15</v>
       </c>
       <c r="C8" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D8" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="1"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5">
         <f>IF((D8-E8)&lt;0,0,(D8-E8))</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="I8" s="5">
         <f>IF((E8-D8)&lt;0,0,(E8-D8))</f>
@@ -14810,14 +14630,14 @@
       </c>
       <c r="J8" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="1"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5">
         <f t="shared" si="2"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="O8" s="5">
         <f t="shared" si="3"/>
@@ -14825,14 +14645,14 @@
       </c>
       <c r="P8" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="Q8" s="5"/>
       <c r="R8" s="1"/>
       <c r="S8" s="5"/>
       <c r="T8" s="5">
         <f t="shared" si="4"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="5"/>
@@ -14840,14 +14660,14 @@
       </c>
       <c r="V8" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="W8" s="5"/>
       <c r="X8" s="1"/>
       <c r="Y8" s="5"/>
       <c r="Z8" s="5">
         <f t="shared" si="6"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="AA8" s="5">
         <f t="shared" si="7"/>
@@ -14862,18 +14682,18 @@
         <v>16</v>
       </c>
       <c r="C9" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D9" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="1"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5">
         <f>IF((D9-E9)&lt;0,0,(D9-E9))</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="I9" s="5">
         <f>IF((E9-D9)&lt;0,0,(E9-D9))</f>
@@ -14881,14 +14701,14 @@
       </c>
       <c r="J9" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="K9" s="5"/>
       <c r="L9" s="1"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5">
         <f t="shared" si="2"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="O9" s="5">
         <f t="shared" si="3"/>
@@ -14896,14 +14716,14 @@
       </c>
       <c r="P9" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="Q9" s="5"/>
       <c r="R9" s="1"/>
       <c r="S9" s="5"/>
       <c r="T9" s="5">
         <f t="shared" si="4"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="5"/>
@@ -14911,14 +14731,14 @@
       </c>
       <c r="V9" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="W9" s="5"/>
       <c r="X9" s="1"/>
       <c r="Y9" s="5"/>
       <c r="Z9" s="5">
         <f t="shared" si="6"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="AA9" s="5">
         <f t="shared" si="7"/>
@@ -14933,18 +14753,18 @@
         <v>62</v>
       </c>
       <c r="C10" s="1">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D10" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="1"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5">
         <f>IF((D10-E10)&lt;0,0,(D10-E10))</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="I10" s="5">
         <f>IF((E10-D10)&lt;0,0,(E10-D10))</f>
@@ -14952,14 +14772,14 @@
       </c>
       <c r="J10" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="1"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5">
         <f t="shared" si="2"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="O10" s="5">
         <f t="shared" si="3"/>
@@ -14967,14 +14787,14 @@
       </c>
       <c r="P10" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="Q10" s="5"/>
       <c r="R10" s="1"/>
       <c r="S10" s="5"/>
       <c r="T10" s="5">
         <f t="shared" si="4"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="5"/>
@@ -14982,14 +14802,14 @@
       </c>
       <c r="V10" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="W10" s="5"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="5"/>
       <c r="Z10" s="5">
         <f t="shared" si="6"/>
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="AA10" s="5">
         <f t="shared" si="7"/>
@@ -15005,18 +14825,18 @@
         <v>8</v>
       </c>
       <c r="C12" s="1">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D12" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="1"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5">
         <f t="shared" si="0"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="1"/>
@@ -15024,14 +14844,14 @@
       </c>
       <c r="J12" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="1"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5">
         <f t="shared" si="2"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="O12" s="5">
         <f t="shared" si="3"/>
@@ -15039,14 +14859,14 @@
       </c>
       <c r="P12" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="Q12" s="5"/>
       <c r="R12" s="1"/>
       <c r="S12" s="5"/>
       <c r="T12" s="5">
         <f t="shared" si="4"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="U12" s="5">
         <f t="shared" si="5"/>
@@ -15054,14 +14874,14 @@
       </c>
       <c r="V12" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="W12" s="5"/>
       <c r="X12" s="1"/>
       <c r="Y12" s="5"/>
       <c r="Z12" s="5">
         <f t="shared" si="6"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="AA12" s="5">
         <f t="shared" si="7"/>
@@ -15076,18 +14896,18 @@
         <v>10</v>
       </c>
       <c r="C13" s="1">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D13" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="1"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5">
         <f t="shared" si="0"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="1"/>
@@ -15095,14 +14915,14 @@
       </c>
       <c r="J13" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="K13" s="5"/>
       <c r="L13" s="1"/>
       <c r="M13" s="5"/>
       <c r="N13" s="5">
         <f t="shared" si="2"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="O13" s="5">
         <f t="shared" si="3"/>
@@ -15110,14 +14930,14 @@
       </c>
       <c r="P13" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="Q13" s="5"/>
       <c r="R13" s="1"/>
       <c r="S13" s="5"/>
       <c r="T13" s="5">
         <f t="shared" si="4"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="U13" s="5">
         <f t="shared" si="5"/>
@@ -15125,14 +14945,14 @@
       </c>
       <c r="V13" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="W13" s="5"/>
       <c r="X13" s="1"/>
       <c r="Y13" s="5"/>
       <c r="Z13" s="5">
         <f t="shared" si="6"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="AA13" s="5">
         <f t="shared" si="7"/>
@@ -15147,11 +14967,11 @@
         <v>11</v>
       </c>
       <c r="C14" s="1">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D14" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="E14" s="5">
         <v>158</v>
@@ -15164,7 +14984,7 @@
       </c>
       <c r="H14" s="5">
         <f t="shared" si="0"/>
-        <v>1346</v>
+        <v>1354</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="1"/>
@@ -15172,14 +14992,14 @@
       </c>
       <c r="J14" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="K14" s="5"/>
       <c r="L14" s="1"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5">
         <f t="shared" si="2"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="O14" s="5">
         <f t="shared" si="3"/>
@@ -15187,14 +15007,14 @@
       </c>
       <c r="P14" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="Q14" s="5"/>
       <c r="R14" s="1"/>
       <c r="S14" s="5"/>
       <c r="T14" s="5">
         <f t="shared" si="4"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="U14" s="5">
         <f t="shared" si="5"/>
@@ -15202,14 +15022,14 @@
       </c>
       <c r="V14" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="W14" s="5"/>
       <c r="X14" s="1"/>
       <c r="Y14" s="5"/>
       <c r="Z14" s="5">
         <f t="shared" si="6"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="AA14" s="5">
         <f t="shared" si="7"/>
@@ -15224,18 +15044,18 @@
         <v>12</v>
       </c>
       <c r="C15" s="1">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D15" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="1"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5">
         <f t="shared" si="0"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="1"/>
@@ -15243,14 +15063,14 @@
       </c>
       <c r="J15" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="K15" s="5"/>
       <c r="L15" s="1"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5">
         <f t="shared" si="2"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="O15" s="5">
         <f t="shared" si="3"/>
@@ -15258,14 +15078,14 @@
       </c>
       <c r="P15" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="Q15" s="5"/>
       <c r="R15" s="1"/>
       <c r="S15" s="5"/>
       <c r="T15" s="5">
         <f t="shared" si="4"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="U15" s="5">
         <f t="shared" si="5"/>
@@ -15273,14 +15093,14 @@
       </c>
       <c r="V15" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="W15" s="5"/>
       <c r="X15" s="1"/>
       <c r="Y15" s="5"/>
       <c r="Z15" s="5">
         <f t="shared" si="6"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="AA15" s="5">
         <f t="shared" si="7"/>
@@ -15295,18 +15115,18 @@
         <v>13</v>
       </c>
       <c r="C16" s="1">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D16" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="1"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5">
         <f t="shared" si="0"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" si="1"/>
@@ -15314,14 +15134,14 @@
       </c>
       <c r="J16" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="K16" s="5"/>
       <c r="L16" s="1"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5">
         <f t="shared" si="2"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="O16" s="5">
         <f t="shared" si="3"/>
@@ -15329,14 +15149,14 @@
       </c>
       <c r="P16" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="Q16" s="5"/>
       <c r="R16" s="1"/>
       <c r="S16" s="5"/>
       <c r="T16" s="5">
         <f t="shared" si="4"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="U16" s="5">
         <f t="shared" si="5"/>
@@ -15344,7 +15164,7 @@
       </c>
       <c r="V16" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="W16" s="5">
         <v>500</v>
@@ -15357,7 +15177,7 @@
       </c>
       <c r="Z16" s="5">
         <f t="shared" si="6"/>
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="AA16" s="5">
         <f t="shared" si="7"/>
@@ -15372,11 +15192,11 @@
         <v>16</v>
       </c>
       <c r="C17" s="1">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D17" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="E17" s="5">
         <v>158</v>
@@ -15389,7 +15209,7 @@
       </c>
       <c r="H17" s="5">
         <f>IF((D17-E17)&lt;0,0,(D17-E17))</f>
-        <v>1346</v>
+        <v>1354</v>
       </c>
       <c r="I17" s="5">
         <f>IF((E17-D17)&lt;0,0,(E17-D17))</f>
@@ -15397,14 +15217,14 @@
       </c>
       <c r="J17" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="K17" s="5"/>
       <c r="L17" s="1"/>
       <c r="M17" s="5"/>
       <c r="N17" s="5">
         <f t="shared" si="2"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="O17" s="5">
         <f t="shared" si="3"/>
@@ -15412,14 +15232,14 @@
       </c>
       <c r="P17" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="Q17" s="5"/>
       <c r="R17" s="1"/>
       <c r="S17" s="5"/>
       <c r="T17" s="5">
         <f t="shared" si="4"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="U17" s="5">
         <f t="shared" si="5"/>
@@ -15427,7 +15247,7 @@
       </c>
       <c r="V17" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="W17" s="5">
         <v>500</v>
@@ -15440,7 +15260,7 @@
       </c>
       <c r="Z17" s="5">
         <f t="shared" si="6"/>
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" si="7"/>
@@ -15455,11 +15275,11 @@
         <v>15</v>
       </c>
       <c r="C18" s="1">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D18" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="E18" s="5">
         <v>158</v>
@@ -15472,7 +15292,7 @@
       </c>
       <c r="H18" s="5">
         <f>IF((D18-E18)&lt;0,0,(D18-E18))</f>
-        <v>1346</v>
+        <v>1354</v>
       </c>
       <c r="I18" s="5">
         <f>IF((E18-D18)&lt;0,0,(E18-D18))</f>
@@ -15480,14 +15300,14 @@
       </c>
       <c r="J18" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="K18" s="5"/>
       <c r="L18" s="1"/>
       <c r="M18" s="5"/>
       <c r="N18" s="5">
         <f t="shared" si="2"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="O18" s="5">
         <f t="shared" si="3"/>
@@ -15495,14 +15315,14 @@
       </c>
       <c r="P18" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="Q18" s="5"/>
       <c r="R18" s="1"/>
       <c r="S18" s="5"/>
       <c r="T18" s="5">
         <f t="shared" si="4"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="U18" s="5">
         <f t="shared" si="5"/>
@@ -15510,7 +15330,7 @@
       </c>
       <c r="V18" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="W18" s="5">
         <v>240</v>
@@ -15523,7 +15343,7 @@
       </c>
       <c r="Z18" s="5">
         <f t="shared" si="6"/>
-        <v>1264</v>
+        <v>1272</v>
       </c>
       <c r="AA18" s="5">
         <f t="shared" si="7"/>
@@ -15538,18 +15358,18 @@
         <v>62</v>
       </c>
       <c r="C19" s="1">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D19" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="1"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5">
         <f>IF((D19-E19)&lt;0,0,(D19-E19))</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="I19" s="5">
         <f>IF((E19-D19)&lt;0,0,(E19-D19))</f>
@@ -15557,14 +15377,14 @@
       </c>
       <c r="J19" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="K19" s="5"/>
       <c r="L19" s="1"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5">
         <f t="shared" si="2"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="O19" s="5">
         <f t="shared" si="3"/>
@@ -15572,14 +15392,14 @@
       </c>
       <c r="P19" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="Q19" s="5"/>
       <c r="R19" s="1"/>
       <c r="S19" s="5"/>
       <c r="T19" s="5">
         <f t="shared" si="4"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="U19" s="5">
         <f t="shared" si="5"/>
@@ -15587,14 +15407,14 @@
       </c>
       <c r="V19" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="W19" s="5"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="5"/>
       <c r="Z19" s="5">
         <f t="shared" si="6"/>
-        <v>1504</v>
+        <v>1512</v>
       </c>
       <c r="AA19" s="5">
         <f t="shared" si="7"/>
@@ -15610,18 +15430,18 @@
         <v>8</v>
       </c>
       <c r="C21" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D21" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="1"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5">
         <f t="shared" si="0"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="I21" s="5">
         <f t="shared" si="1"/>
@@ -15629,14 +15449,14 @@
       </c>
       <c r="J21" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="K21" s="5"/>
       <c r="L21" s="1"/>
       <c r="M21" s="5"/>
       <c r="N21" s="5">
         <f t="shared" si="2"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="O21" s="5">
         <f t="shared" si="3"/>
@@ -15644,14 +15464,14 @@
       </c>
       <c r="P21" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="Q21" s="5"/>
       <c r="R21" s="1"/>
       <c r="S21" s="5"/>
       <c r="T21" s="5">
         <f t="shared" si="4"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="U21" s="5">
         <f t="shared" si="5"/>
@@ -15659,14 +15479,14 @@
       </c>
       <c r="V21" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="W21" s="5"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="5"/>
       <c r="Z21" s="5">
         <f t="shared" si="6"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="AA21" s="5">
         <f t="shared" si="7"/>
@@ -15681,18 +15501,18 @@
         <v>10</v>
       </c>
       <c r="C22" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D22" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="1"/>
       <c r="G22" s="5"/>
       <c r="H22" s="5">
         <f t="shared" si="0"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="I22" s="5">
         <f t="shared" si="1"/>
@@ -15700,14 +15520,14 @@
       </c>
       <c r="J22" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="K22" s="5"/>
       <c r="L22" s="1"/>
       <c r="M22" s="5"/>
       <c r="N22" s="5">
         <f t="shared" si="2"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="O22" s="5">
         <f t="shared" si="3"/>
@@ -15715,14 +15535,14 @@
       </c>
       <c r="P22" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="Q22" s="5"/>
       <c r="R22" s="1"/>
       <c r="S22" s="5"/>
       <c r="T22" s="5">
         <f t="shared" si="4"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="U22" s="5">
         <f t="shared" si="5"/>
@@ -15730,14 +15550,14 @@
       </c>
       <c r="V22" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="W22" s="5"/>
       <c r="X22" s="1"/>
       <c r="Y22" s="5"/>
       <c r="Z22" s="5">
         <f t="shared" si="6"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="AA22" s="5">
         <f t="shared" si="7"/>
@@ -15752,18 +15572,18 @@
         <v>11</v>
       </c>
       <c r="C23" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D23" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="1"/>
       <c r="G23" s="5"/>
       <c r="H23" s="5">
         <f t="shared" si="0"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="I23" s="5">
         <f t="shared" si="1"/>
@@ -15771,14 +15591,14 @@
       </c>
       <c r="J23" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="K23" s="5"/>
       <c r="L23" s="1"/>
       <c r="M23" s="5"/>
       <c r="N23" s="5">
         <f t="shared" si="2"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="O23" s="5">
         <f t="shared" si="3"/>
@@ -15786,14 +15606,14 @@
       </c>
       <c r="P23" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="Q23" s="5"/>
       <c r="R23" s="1"/>
       <c r="S23" s="5"/>
       <c r="T23" s="5">
         <f t="shared" si="4"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="U23" s="5">
         <f t="shared" si="5"/>
@@ -15801,14 +15621,14 @@
       </c>
       <c r="V23" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="W23" s="5"/>
       <c r="X23" s="1"/>
       <c r="Y23" s="5"/>
       <c r="Z23" s="5">
         <f t="shared" si="6"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="AA23" s="5">
         <f t="shared" si="7"/>
@@ -15823,11 +15643,11 @@
         <v>14</v>
       </c>
       <c r="C24" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D24" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="E24" s="5">
         <v>105</v>
@@ -15840,7 +15660,7 @@
       </c>
       <c r="H24" s="5">
         <f t="shared" si="0"/>
-        <v>1151</v>
+        <v>1143</v>
       </c>
       <c r="I24" s="5">
         <f t="shared" si="1"/>
@@ -15848,14 +15668,14 @@
       </c>
       <c r="J24" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="K24" s="5"/>
       <c r="L24" s="1"/>
       <c r="M24" s="5"/>
       <c r="N24" s="5">
         <f t="shared" si="2"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="O24" s="5">
         <f t="shared" si="3"/>
@@ -15863,14 +15683,14 @@
       </c>
       <c r="P24" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="Q24" s="5"/>
       <c r="R24" s="1"/>
       <c r="S24" s="5"/>
       <c r="T24" s="5">
         <f t="shared" si="4"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="U24" s="5">
         <f t="shared" si="5"/>
@@ -15878,14 +15698,14 @@
       </c>
       <c r="V24" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="W24" s="5"/>
       <c r="X24" s="1"/>
       <c r="Y24" s="5"/>
       <c r="Z24" s="5">
         <f t="shared" si="6"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="AA24" s="5">
         <f t="shared" si="7"/>
@@ -15900,11 +15720,11 @@
         <v>12</v>
       </c>
       <c r="C25" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D25" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="E25" s="5">
         <v>105</v>
@@ -15917,7 +15737,7 @@
       </c>
       <c r="H25" s="5">
         <f t="shared" si="0"/>
-        <v>1151</v>
+        <v>1143</v>
       </c>
       <c r="I25" s="5">
         <f t="shared" si="1"/>
@@ -15925,14 +15745,14 @@
       </c>
       <c r="J25" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="K25" s="5"/>
       <c r="L25" s="1"/>
       <c r="M25" s="5"/>
       <c r="N25" s="5">
         <f t="shared" si="2"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="O25" s="5">
         <f t="shared" si="3"/>
@@ -15940,14 +15760,14 @@
       </c>
       <c r="P25" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="Q25" s="5"/>
       <c r="R25" s="1"/>
       <c r="S25" s="5"/>
       <c r="T25" s="5">
         <f t="shared" si="4"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="U25" s="5">
         <f t="shared" si="5"/>
@@ -15955,14 +15775,14 @@
       </c>
       <c r="V25" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="W25" s="5"/>
       <c r="X25" s="1"/>
       <c r="Y25" s="5"/>
       <c r="Z25" s="5">
         <f t="shared" si="6"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="AA25" s="5">
         <f t="shared" si="7"/>
@@ -15977,11 +15797,11 @@
         <v>13</v>
       </c>
       <c r="C26" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D26" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="E26" s="5">
         <v>105</v>
@@ -15994,7 +15814,7 @@
       </c>
       <c r="H26" s="5">
         <f t="shared" si="0"/>
-        <v>1151</v>
+        <v>1143</v>
       </c>
       <c r="I26" s="5">
         <f t="shared" si="1"/>
@@ -16002,14 +15822,14 @@
       </c>
       <c r="J26" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="K26" s="5"/>
       <c r="L26" s="1"/>
       <c r="M26" s="5"/>
       <c r="N26" s="5">
         <f t="shared" si="2"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="O26" s="5">
         <f t="shared" si="3"/>
@@ -16017,14 +15837,14 @@
       </c>
       <c r="P26" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="Q26" s="5"/>
       <c r="R26" s="1"/>
       <c r="S26" s="5"/>
       <c r="T26" s="5">
         <f t="shared" si="4"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="U26" s="5">
         <f t="shared" si="5"/>
@@ -16032,7 +15852,7 @@
       </c>
       <c r="V26" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="W26" s="5">
         <v>700</v>
@@ -16045,7 +15865,7 @@
       </c>
       <c r="Z26" s="5">
         <f t="shared" si="6"/>
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="AA26" s="5">
         <f t="shared" si="7"/>
@@ -16060,11 +15880,11 @@
         <v>15</v>
       </c>
       <c r="C27" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D27" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="E27" s="5">
         <v>105</v>
@@ -16077,7 +15897,7 @@
       </c>
       <c r="H27" s="5">
         <f>IF((D27-E27)&lt;0,0,(D27-E27))</f>
-        <v>1151</v>
+        <v>1143</v>
       </c>
       <c r="I27" s="5">
         <f>IF((E27-D27)&lt;0,0,(E27-D27))</f>
@@ -16085,14 +15905,14 @@
       </c>
       <c r="J27" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="K27" s="5"/>
       <c r="L27" s="1"/>
       <c r="M27" s="5"/>
       <c r="N27" s="5">
         <f t="shared" si="2"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="O27" s="5">
         <f t="shared" si="3"/>
@@ -16100,14 +15920,14 @@
       </c>
       <c r="P27" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="Q27" s="5"/>
       <c r="R27" s="1"/>
       <c r="S27" s="5"/>
       <c r="T27" s="5">
         <f t="shared" si="4"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="U27" s="5">
         <f t="shared" si="5"/>
@@ -16115,7 +15935,7 @@
       </c>
       <c r="V27" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="W27" s="5">
         <v>550</v>
@@ -16128,7 +15948,7 @@
       </c>
       <c r="Z27" s="5">
         <f t="shared" si="6"/>
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="AA27" s="5">
         <f t="shared" si="7"/>
@@ -16143,18 +15963,18 @@
         <v>16</v>
       </c>
       <c r="C28" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D28" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="1"/>
       <c r="G28" s="5"/>
       <c r="H28" s="5">
         <f>IF((D28-E28)&lt;0,0,(D28-E28))</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="I28" s="5">
         <f>IF((E28-D28)&lt;0,0,(E28-D28))</f>
@@ -16162,14 +15982,14 @@
       </c>
       <c r="J28" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="K28" s="5"/>
       <c r="L28" s="1"/>
       <c r="M28" s="5"/>
       <c r="N28" s="5">
         <f t="shared" si="2"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="O28" s="5">
         <f t="shared" si="3"/>
@@ -16177,14 +15997,14 @@
       </c>
       <c r="P28" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="Q28" s="5"/>
       <c r="R28" s="1"/>
       <c r="S28" s="5"/>
       <c r="T28" s="5">
         <f t="shared" si="4"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="U28" s="5">
         <f t="shared" si="5"/>
@@ -16192,7 +16012,7 @@
       </c>
       <c r="V28" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="W28" s="5">
         <v>400</v>
@@ -16205,7 +16025,7 @@
       </c>
       <c r="Z28" s="5">
         <f t="shared" si="6"/>
-        <v>856</v>
+        <v>848</v>
       </c>
       <c r="AA28" s="5">
         <f t="shared" si="7"/>
@@ -16220,18 +16040,18 @@
         <v>62</v>
       </c>
       <c r="C29" s="1">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D29" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="1"/>
       <c r="G29" s="5"/>
       <c r="H29" s="5">
         <f>IF((D29-E29)&lt;0,0,(D29-E29))</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="I29" s="5">
         <f>IF((E29-D29)&lt;0,0,(E29-D29))</f>
@@ -16239,14 +16059,14 @@
       </c>
       <c r="J29" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="K29" s="5"/>
       <c r="L29" s="1"/>
       <c r="M29" s="5"/>
       <c r="N29" s="5">
         <f t="shared" si="2"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="O29" s="5">
         <f t="shared" si="3"/>
@@ -16254,14 +16074,14 @@
       </c>
       <c r="P29" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="Q29" s="5"/>
       <c r="R29" s="1"/>
       <c r="S29" s="5"/>
       <c r="T29" s="5">
         <f t="shared" si="4"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="U29" s="5">
         <f t="shared" si="5"/>
@@ -16269,14 +16089,14 @@
       </c>
       <c r="V29" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="W29" s="5"/>
       <c r="X29" s="1"/>
       <c r="Y29" s="5"/>
       <c r="Z29" s="5">
         <f t="shared" si="6"/>
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="AA29" s="5">
         <f t="shared" si="7"/>
@@ -17092,18 +16912,18 @@
         <v>15</v>
       </c>
       <c r="C43" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D43" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="1"/>
       <c r="G43" s="5"/>
       <c r="H43" s="5">
         <f t="shared" si="0"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="I43" s="5">
         <f t="shared" si="1"/>
@@ -17111,14 +16931,14 @@
       </c>
       <c r="J43" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="K43" s="5"/>
       <c r="L43" s="1"/>
       <c r="M43" s="5"/>
       <c r="N43" s="5">
         <f t="shared" si="2"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="O43" s="5">
         <f t="shared" si="3"/>
@@ -17126,14 +16946,14 @@
       </c>
       <c r="P43" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="Q43" s="5"/>
       <c r="R43" s="1"/>
       <c r="S43" s="5"/>
       <c r="T43" s="5">
         <f t="shared" si="4"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="U43" s="5">
         <f t="shared" si="5"/>
@@ -17141,14 +16961,14 @@
       </c>
       <c r="V43" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="W43" s="5"/>
       <c r="X43" s="1"/>
       <c r="Y43" s="5"/>
       <c r="Z43" s="5">
         <f t="shared" si="6"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="AA43" s="5">
         <f t="shared" si="7"/>
@@ -17163,18 +16983,18 @@
         <v>16</v>
       </c>
       <c r="C44" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D44" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="1"/>
       <c r="G44" s="5"/>
       <c r="H44" s="5">
         <f t="shared" si="0"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="I44" s="5">
         <f t="shared" si="1"/>
@@ -17182,14 +17002,14 @@
       </c>
       <c r="J44" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="K44" s="5"/>
       <c r="L44" s="1"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5">
         <f t="shared" si="2"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="O44" s="5">
         <f t="shared" si="3"/>
@@ -17197,14 +17017,14 @@
       </c>
       <c r="P44" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="Q44" s="5"/>
       <c r="R44" s="1"/>
       <c r="S44" s="5"/>
       <c r="T44" s="5">
         <f t="shared" si="4"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="U44" s="5">
         <f t="shared" si="5"/>
@@ -17212,14 +17032,14 @@
       </c>
       <c r="V44" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="W44" s="5"/>
       <c r="X44" s="1"/>
       <c r="Y44" s="5"/>
       <c r="Z44" s="5">
         <f t="shared" si="6"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="AA44" s="5">
         <f t="shared" si="7"/>
@@ -17234,18 +17054,18 @@
         <v>13</v>
       </c>
       <c r="C45" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D45" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="1"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5">
         <f t="shared" si="0"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="I45" s="5">
         <f t="shared" si="1"/>
@@ -17253,14 +17073,14 @@
       </c>
       <c r="J45" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="K45" s="5"/>
       <c r="L45" s="1"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5">
         <f t="shared" si="2"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="O45" s="5">
         <f t="shared" si="3"/>
@@ -17268,14 +17088,14 @@
       </c>
       <c r="P45" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="Q45" s="5"/>
       <c r="R45" s="1"/>
       <c r="S45" s="5"/>
       <c r="T45" s="5">
         <f t="shared" si="4"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="U45" s="5">
         <f t="shared" si="5"/>
@@ -17283,14 +17103,14 @@
       </c>
       <c r="V45" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="W45" s="5"/>
       <c r="X45" s="1"/>
       <c r="Y45" s="5"/>
       <c r="Z45" s="5">
         <f t="shared" si="6"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="AA45" s="5">
         <f t="shared" si="7"/>
@@ -17305,18 +17125,18 @@
         <v>11</v>
       </c>
       <c r="C46" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D46" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="1"/>
       <c r="G46" s="5"/>
       <c r="H46" s="5">
         <f t="shared" si="0"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" si="1"/>
@@ -17324,14 +17144,14 @@
       </c>
       <c r="J46" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="K46" s="5"/>
       <c r="L46" s="1"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5">
         <f t="shared" si="2"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="O46" s="5">
         <f t="shared" si="3"/>
@@ -17339,14 +17159,14 @@
       </c>
       <c r="P46" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="Q46" s="5"/>
       <c r="R46" s="1"/>
       <c r="S46" s="5"/>
       <c r="T46" s="5">
         <f t="shared" si="4"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="U46" s="5">
         <f t="shared" si="5"/>
@@ -17354,14 +17174,14 @@
       </c>
       <c r="V46" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="W46" s="5"/>
       <c r="X46" s="1"/>
       <c r="Y46" s="5"/>
       <c r="Z46" s="5">
         <f t="shared" si="6"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="AA46" s="5">
         <f t="shared" si="7"/>
@@ -17376,18 +17196,18 @@
         <v>17</v>
       </c>
       <c r="C47" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D47" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="1"/>
       <c r="G47" s="5"/>
       <c r="H47" s="5">
         <f t="shared" si="0"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="I47" s="5">
         <f t="shared" si="1"/>
@@ -17395,14 +17215,14 @@
       </c>
       <c r="J47" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="K47" s="5"/>
       <c r="L47" s="1"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5">
         <f t="shared" si="2"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="O47" s="5">
         <f t="shared" si="3"/>
@@ -17410,14 +17230,14 @@
       </c>
       <c r="P47" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="Q47" s="5"/>
       <c r="R47" s="1"/>
       <c r="S47" s="5"/>
       <c r="T47" s="5">
         <f t="shared" si="4"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="U47" s="5">
         <f t="shared" si="5"/>
@@ -17425,14 +17245,14 @@
       </c>
       <c r="V47" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="W47" s="5"/>
       <c r="X47" s="1"/>
       <c r="Y47" s="5"/>
       <c r="Z47" s="5">
         <f t="shared" si="6"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="AA47" s="5">
         <f t="shared" si="7"/>
@@ -17447,18 +17267,18 @@
         <v>14</v>
       </c>
       <c r="C48" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D48" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="1"/>
       <c r="G48" s="5"/>
       <c r="H48" s="5">
         <f t="shared" si="0"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="I48" s="5">
         <f t="shared" si="1"/>
@@ -17466,14 +17286,14 @@
       </c>
       <c r="J48" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="K48" s="5"/>
       <c r="L48" s="1"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5">
         <f t="shared" ref="N48:N53" si="10">IF((J48-K48)&lt;0,0,(J48-K48))</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="O48" s="5">
         <f t="shared" ref="O48:O53" si="11">IF((K48-J48)&lt;0,0,(K48-J48))</f>
@@ -17481,14 +17301,14 @@
       </c>
       <c r="P48" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="Q48" s="5"/>
       <c r="R48" s="1"/>
       <c r="S48" s="5"/>
       <c r="T48" s="5">
         <f t="shared" si="4"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="U48" s="5">
         <f t="shared" si="5"/>
@@ -17496,14 +17316,14 @@
       </c>
       <c r="V48" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="W48" s="5"/>
       <c r="X48" s="1"/>
       <c r="Y48" s="5"/>
       <c r="Z48" s="5">
         <f t="shared" si="6"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="AA48" s="5">
         <f t="shared" si="7"/>
@@ -17518,18 +17338,18 @@
         <v>87</v>
       </c>
       <c r="C49" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D49" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="1"/>
       <c r="G49" s="5"/>
       <c r="H49" s="5">
         <f>IF((D49-E49)&lt;0,0,(D49-E49))</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="I49" s="5">
         <f>IF((E49-D49)&lt;0,0,(E49-D49))</f>
@@ -17537,14 +17357,14 @@
       </c>
       <c r="J49" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="K49" s="5"/>
       <c r="L49" s="1"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5">
         <f t="shared" si="10"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="O49" s="5">
         <f t="shared" si="11"/>
@@ -17552,14 +17372,14 @@
       </c>
       <c r="P49" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="Q49" s="5"/>
       <c r="R49" s="1"/>
       <c r="S49" s="5"/>
       <c r="T49" s="5">
         <f>IF((P49-Q49)&lt;0,0,(P49-Q49))</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="U49" s="5">
         <f>IF((Q49-P49)&lt;0,0,(Q49-P49))</f>
@@ -17567,14 +17387,14 @@
       </c>
       <c r="V49" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="W49" s="5"/>
       <c r="X49" s="1"/>
       <c r="Y49" s="5"/>
       <c r="Z49" s="5">
         <f>IF((V49-W49)&lt;0,0,(V49-W49))</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="AA49" s="5">
         <f>IF((W49-V49)&lt;0,0,(W49-V49))</f>
@@ -17589,18 +17409,18 @@
         <v>88</v>
       </c>
       <c r="C50" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D50" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="1"/>
       <c r="G50" s="5"/>
       <c r="H50" s="5">
         <f t="shared" si="0"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="I50" s="5">
         <f t="shared" si="1"/>
@@ -17608,14 +17428,14 @@
       </c>
       <c r="J50" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="K50" s="5"/>
       <c r="L50" s="1"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5">
         <f t="shared" si="10"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="O50" s="5">
         <f t="shared" si="11"/>
@@ -17623,14 +17443,14 @@
       </c>
       <c r="P50" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="Q50" s="5"/>
       <c r="R50" s="1"/>
       <c r="S50" s="5"/>
       <c r="T50" s="5">
         <f t="shared" si="4"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="U50" s="5">
         <f t="shared" si="5"/>
@@ -17638,14 +17458,14 @@
       </c>
       <c r="V50" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="W50" s="5"/>
       <c r="X50" s="1"/>
       <c r="Y50" s="5"/>
       <c r="Z50" s="5">
         <f t="shared" si="6"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="AA50" s="5">
         <f t="shared" si="7"/>
@@ -17660,18 +17480,18 @@
         <v>19</v>
       </c>
       <c r="C51" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D51" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="1"/>
       <c r="G51" s="5"/>
       <c r="H51" s="5">
         <f t="shared" si="0"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="I51" s="5">
         <f t="shared" si="1"/>
@@ -17679,14 +17499,14 @@
       </c>
       <c r="J51" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="K51" s="5"/>
       <c r="L51" s="1"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5">
         <f t="shared" si="10"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="O51" s="5">
         <f t="shared" si="11"/>
@@ -17694,14 +17514,14 @@
       </c>
       <c r="P51" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="Q51" s="5"/>
       <c r="R51" s="1"/>
       <c r="S51" s="5"/>
       <c r="T51" s="5">
         <f t="shared" si="4"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="U51" s="5">
         <f t="shared" si="5"/>
@@ -17709,14 +17529,14 @@
       </c>
       <c r="V51" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="W51" s="5"/>
       <c r="X51" s="1"/>
       <c r="Y51" s="5"/>
       <c r="Z51" s="5">
         <f t="shared" si="6"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="AA51" s="5">
         <f t="shared" si="7"/>
@@ -17731,18 +17551,18 @@
         <v>89</v>
       </c>
       <c r="C52" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D52" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="E52" s="5"/>
       <c r="F52" s="1"/>
       <c r="G52" s="5"/>
       <c r="H52" s="5">
         <f>IF((D52-E52)&lt;0,0,(D52-E52))</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="I52" s="5">
         <f>IF((E52-D52)&lt;0,0,(E52-D52))</f>
@@ -17750,14 +17570,14 @@
       </c>
       <c r="J52" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="K52" s="5"/>
       <c r="L52" s="1"/>
       <c r="M52" s="5"/>
       <c r="N52" s="5">
         <f t="shared" si="10"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="O52" s="5">
         <f t="shared" si="11"/>
@@ -17765,14 +17585,14 @@
       </c>
       <c r="P52" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="Q52" s="5"/>
       <c r="R52" s="1"/>
       <c r="S52" s="5"/>
       <c r="T52" s="5">
         <f>IF((P52-Q52)&lt;0,0,(P52-Q52))</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="U52" s="5">
         <f>IF((Q52-P52)&lt;0,0,(Q52-P52))</f>
@@ -17780,14 +17600,14 @@
       </c>
       <c r="V52" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="W52" s="5"/>
       <c r="X52" s="1"/>
       <c r="Y52" s="5"/>
       <c r="Z52" s="5">
         <f>IF((V52-W52)&lt;0,0,(V52-W52))</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="AA52" s="5">
         <f>IF((W52-V52)&lt;0,0,(W52-V52))</f>
@@ -17802,18 +17622,18 @@
         <v>90</v>
       </c>
       <c r="C53" s="1">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D53" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="E53" s="5"/>
       <c r="F53" s="1"/>
       <c r="G53" s="5"/>
       <c r="H53" s="5">
         <f t="shared" si="0"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="I53" s="5">
         <f t="shared" si="1"/>
@@ -17821,14 +17641,14 @@
       </c>
       <c r="J53" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="K53" s="5"/>
       <c r="L53" s="1"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5">
         <f t="shared" si="10"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="O53" s="5">
         <f t="shared" si="11"/>
@@ -17836,14 +17656,14 @@
       </c>
       <c r="P53" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="Q53" s="5"/>
       <c r="R53" s="1"/>
       <c r="S53" s="5"/>
       <c r="T53" s="5">
         <f t="shared" si="4"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="U53" s="5">
         <f t="shared" si="5"/>
@@ -17851,14 +17671,14 @@
       </c>
       <c r="V53" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="W53" s="5"/>
       <c r="X53" s="1"/>
       <c r="Y53" s="5"/>
       <c r="Z53" s="5">
         <f t="shared" si="6"/>
-        <v>1424</v>
+        <v>1408</v>
       </c>
       <c r="AA53" s="5">
         <f t="shared" si="7"/>
@@ -22957,189 +22777,9 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C91:C101 C103:C113 C115:C122" name="Textbooks"/>
+    <protectedRange sqref="C31:C41 C55:C65 C67:C77 C79:C89 C91:C101 C103:C113 C115:C122 C2:C10 C12:C19 C21:C29 C43:C53" name="Textbooks"/>
     <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113" name="LAS"/>
     <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122" name="SOURCE"/>
   </protectedRanges>
@@ -23154,8 +22794,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
